--- a/tests/workbooktests/workbooks/test_gaussian1dmodel.xlsx
+++ b/tests/workbooktests/workbooks/test_gaussian1dmodel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939C0DD8-CAD3-4101-B458-B3237FFFA754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A211BC-9FBB-4962-BCBB-6ED81D72D173}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{096EF196-26B4-4940-94D5-2518E57D2FCB}"/>
   </bookViews>
@@ -21,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -40,14 +29,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -398,7 +387,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -490,8 +479,8 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -824,14 +813,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19C12335-CBD8-46BF-9EBD-5BF6B0C18873}">
   <dimension ref="A1:E80"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.33203125" customWidth="1"/>
-    <col min="3" max="5" width="24.6640625" customWidth="1"/>
+    <col min="2" max="2" width="35.375" customWidth="1"/>
+    <col min="3" max="5" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -839,25 +828,25 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" cm="1">
+      <c r="B2" s="1">
         <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
         <v>46174</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="str" cm="1">
+      <c r="B4" t="str">
         <f t="array" ref="B4">_xll.qlFlatForward(B2,0.03,"Act/365")</f>
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -875,7 +864,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -892,7 +881,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -909,7 +898,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -917,46 +906,46 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="15">
       <c r="A13" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B13" t="str" cm="1">
+      <c r="B13" t="str">
         <f t="array" ref="B13">_xll.qlGsr(B4,B8:D8,B9:E9,B10:E10,B11)</f>
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R13C2Gsr,A</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="15">
       <c r="A15" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B15" t="str" cm="1">
+      <c r="B15" t="str">
         <f t="array" ref="B15">_xll.qlGaussian1dSwaptionEngine(B13)</f>
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R15C2Gaussian1dSwaptionEngine,A</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="4" t="str" cm="1">
-        <f t="array" ref="B17">_xll.qlFlatForward(B2,0.03)</f>
+      <c r="B17" s="4" t="str">
+        <f>_xll.qlFlatForward(B2,0.03,"actual365fixed")</f>
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R17C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="4" t="str" cm="1">
+      <c r="B18" s="4" t="str">
         <f t="array" ref="B18">_xll.qlEuribor("6M",B17)</f>
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R18C2Euribor,A</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2">
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -964,7 +953,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -972,25 +961,25 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="3" cm="1">
+      <c r="B22" s="3">
         <f t="array" ref="B22">_xll.qlCalendarAdvance("Target",$B$2,B20,"ModifiedFollowing")</f>
         <v>46905</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="3" cm="1">
+      <c r="B23" s="3">
         <f t="array" ref="B23">_xll.qlCalendarAdvance("Target",$B$2,B21,"ModifiedFollowing")</f>
         <v>48001</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -998,141 +987,141 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="4" t="str" cm="1">
+      <c r="B25" s="4" t="str">
         <f t="array" ref="B25">_xll.qlMakeSchedule(B22,B23,"1y",,"Target","ModifiedFollowing",,"Backward")</f>
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R25C2Schedule,A</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="4" t="str" cm="1">
+      <c r="B26" s="4" t="str">
         <f t="array" ref="B26">_xll.qlMakeSchedule(B22,B23,"6m",,"Target","ModifiedFollowing",,"Backward")</f>
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R26C2Schedule,A</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="4" t="str" cm="1">
+      <c r="B27" s="4" t="str">
         <f t="array" ref="B27">_xll.qlVanillaSwap("Payer",10000,B25,B24,"30/360",B26,B18,0,"Act/360")</f>
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R27C2VanillaSwap,A</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2">
       <c r="B28" s="4"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="1" cm="1">
+      <c r="B29" s="1">
         <f t="array" ref="B29:B33">_xll.qlScheduleDates(B25) - 2</f>
         <v>46903</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2">
       <c r="B30" s="3">
         <v>46904</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2">
       <c r="B31" s="3">
         <v>47271</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2">
       <c r="B32" s="3">
         <v>47635</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5">
       <c r="B33" s="6">
         <v>47999</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5">
       <c r="B34" s="4"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="4" t="str" cm="1">
+      <c r="B35" s="4" t="str">
         <f t="array" ref="B35">_xll.qlEuropeanExercise(B29)</f>
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R35C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>23</v>
       </c>
-      <c r="B36" s="4" t="str" cm="1">
+      <c r="B36" s="4" t="str">
         <f t="array" ref="B36">_xll.qlBermudanExercise(B29:B32)</f>
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R36C2BermudanExercise,A</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5">
       <c r="B37" s="4"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>24</v>
       </c>
       <c r="B38" s="4"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>25</v>
       </c>
       <c r="B39" s="4"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5">
       <c r="B40" s="4"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="4" t="str" cm="1">
+      <c r="B41" s="4" t="str">
         <f t="array" ref="B41">_xll.qlSwaption(B27,B35)</f>
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R41C2Swaption,A</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>27</v>
       </c>
-      <c r="B42" s="4" t="str" cm="1">
+      <c r="B42" s="4" t="str">
         <f t="array" ref="B42">_xll.qlSwaption(B27,B36)</f>
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R42C2Swaption,A</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>28</v>
       </c>
-      <c r="B44" cm="1">
+      <c r="B44">
         <f t="array" ref="B44">_xll.qlInstrumentNPV(B41,_xll.qlInstrumentSetPricingEngine(B41,B15))</f>
         <v>126.78027860072075</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>28</v>
       </c>
-      <c r="B45" cm="1">
+      <c r="B45">
         <f t="array" ref="B45">_xll.qlInstrumentNPV(B42,_xll.qlInstrumentSetPricingEngine(B42,B15))</f>
-        <v>143.17547718731561</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+        <v>125.42646852011532</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="15">
       <c r="B48" s="10" t="s">
         <v>29</v>
       </c>
@@ -1146,7 +1135,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
         <v>30</v>
       </c>
@@ -1163,7 +1152,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>32</v>
       </c>
@@ -1180,7 +1169,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
         <v>34</v>
       </c>
@@ -1197,7 +1186,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>35</v>
       </c>
@@ -1218,7 +1207,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R18C2Euribor,A</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
         <v>36</v>
       </c>
@@ -1235,7 +1224,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>38</v>
       </c>
@@ -1252,7 +1241,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
         <v>40</v>
       </c>
@@ -1269,7 +1258,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>42</v>
       </c>
@@ -1290,7 +1279,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
         <v>43</v>
       </c>
@@ -1307,7 +1296,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>45</v>
       </c>
@@ -1324,7 +1313,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
         <v>46</v>
       </c>
@@ -1341,7 +1330,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>47</v>
       </c>
@@ -1358,7 +1347,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>49</v>
       </c>
@@ -1375,7 +1364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>50</v>
       </c>
@@ -1392,7 +1381,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
         <v>51</v>
       </c>
@@ -1409,55 +1398,55 @@
         <v>52</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>29</v>
       </c>
-      <c r="B65" s="4" t="str" cm="1">
+      <c r="B65" s="4" t="str">
         <f t="array" ref="B65">_xll.qlSwaptionHelper(B49,B50,B51,B52,B53,B54,B55,B56,B57,B58,B59,B60,B61,B62)</f>
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R65C2SwaptionHelper,A</v>
       </c>
-      <c r="C65" s="4" t="str" cm="1">
+      <c r="C65" s="4" t="str">
         <f t="array" ref="C65">_xll.qlSwaptionHelper(C49,C50,C51,C52,C53,C54,C55,C56,C57,C58,C59,C60,C61,C62)</f>
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R65C3SwaptionHelper,A</v>
       </c>
-      <c r="D65" s="4" t="str" cm="1">
+      <c r="D65" s="4" t="str">
         <f t="array" ref="D65">_xll.qlSwaptionHelper(D49,D50,D51,D52,D53,D54,D55,D56,D57,D58,D59,D60,D61,D62)</f>
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R65C4SwaptionHelper,A</v>
       </c>
-      <c r="E65" s="4" t="str" cm="1">
+      <c r="E65" s="4" t="str">
         <f t="array" ref="E65">_xll.qlSwaptionHelper(E49,E50,E51,E52,E53,E54,E55,E56,E57,E58,E59,E60,E61,E62)</f>
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R65C5SwaptionHelper,A</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B66" t="b" cm="1">
+    <row r="66" spans="1:5">
+      <c r="B66" t="b">
         <f t="array" ref="B66">_xll.qlBlackCalibrationHelperSetPricingEngine(B65,$B$15)</f>
         <v>1</v>
       </c>
-      <c r="C66" t="b" cm="1">
+      <c r="C66" t="b">
         <f t="array" ref="C66">_xll.qlBlackCalibrationHelperSetPricingEngine(C65,$B$15)</f>
         <v>1</v>
       </c>
-      <c r="D66" t="b" cm="1">
+      <c r="D66" t="b">
         <f t="array" ref="D66">_xll.qlBlackCalibrationHelperSetPricingEngine(D65,$B$15)</f>
         <v>1</v>
       </c>
-      <c r="E66" t="b" cm="1">
+      <c r="E66" t="b">
         <f t="array" ref="E66">_xll.qlBlackCalibrationHelperSetPricingEngine(E65,$B$15)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
         <v>55</v>
       </c>
-      <c r="B68" t="str" cm="1">
+      <c r="B68" t="str">
         <f t="array" ref="B68">_xll.qlLevenbergMarquardt(,,,,B66:E66)</f>
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R68C2LevenbergMarquardt,A</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>56</v>
       </c>
@@ -1465,7 +1454,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
         <v>57</v>
       </c>
@@ -1473,7 +1462,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
         <v>58</v>
       </c>
@@ -1481,7 +1470,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
         <v>59</v>
       </c>
@@ -1489,7 +1478,7 @@
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
         <v>60</v>
       </c>
@@ -1497,29 +1486,29 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
         <v>61</v>
       </c>
-      <c r="B75" t="str" cm="1">
+      <c r="B75" t="str">
         <f t="array" ref="B75">_xll.qlEndCriteria(B70,B71,B72,B73,B74,B66:E66)</f>
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R75C2EndCriteria,A</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5">
       <c r="A77" t="s">
         <v>62</v>
       </c>
-      <c r="B77" t="b" cm="1">
+      <c r="B77" t="b">
         <f t="array" ref="B77">_xll.qlGsrCalibrateVolatilitiesIterative(B13,B65:E65,B68,B75,,,B66:E66)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" ht="15">
       <c r="A79" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B79" cm="1">
+      <c r="B79">
         <f t="array" ref="B79:E79">TRANSPOSE(_xll.qlGsrVolatility(B13,B77))</f>
         <v>6.9631874311834709E-3</v>
       </c>
@@ -1533,11 +1522,11 @@
         <v>6.999176212400815E-3</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" ht="15">
       <c r="A80" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B80" cm="1">
+      <c r="B80">
         <f t="array" ref="B80:E80">TRANSPOSE(_xll.qlGsrReversion(B13,B77))</f>
         <v>0.01</v>
       </c>
@@ -1559,24 +1548,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3DE146D-E077-4092-A23A-A651D070976A}">
   <dimension ref="A1:X62"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" customWidth="1"/>
-    <col min="2" max="2" width="28.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.77734375" customWidth="1"/>
-    <col min="11" max="11" width="14.21875" customWidth="1"/>
-    <col min="15" max="15" width="14.77734375" customWidth="1"/>
-    <col min="16" max="16" width="12.109375" customWidth="1"/>
-    <col min="17" max="18" width="13.5546875" customWidth="1"/>
-    <col min="19" max="19" width="13.109375" customWidth="1"/>
-    <col min="20" max="20" width="18.5546875" customWidth="1"/>
+    <col min="1" max="1" width="20.625" customWidth="1"/>
+    <col min="2" max="2" width="28.625" customWidth="1"/>
+    <col min="4" max="4" width="17.75" customWidth="1"/>
+    <col min="11" max="11" width="14.25" customWidth="1"/>
+    <col min="15" max="15" width="14.75" customWidth="1"/>
+    <col min="16" max="16" width="12.125" customWidth="1"/>
+    <col min="17" max="18" width="13.5" customWidth="1"/>
+    <col min="19" max="19" width="13.125" customWidth="1"/>
+    <col min="20" max="20" width="18.5" customWidth="1"/>
     <col min="21" max="21" width="15" customWidth="1"/>
-    <col min="22" max="22" width="13.21875" customWidth="1"/>
-    <col min="23" max="23" width="11.33203125" customWidth="1"/>
-    <col min="24" max="24" width="10.44140625" customWidth="1"/>
+    <col min="22" max="22" width="13.25" customWidth="1"/>
+    <col min="23" max="23" width="11.375" customWidth="1"/>
+    <col min="24" max="24" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1584,7 +1573,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1593,7 +1582,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24">
       <c r="A4" t="s">
         <v>82</v>
       </c>
@@ -1658,7 +1647,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24">
       <c r="D5" s="12" t="s">
         <v>12</v>
       </c>
@@ -1724,7 +1713,7 @@
         <v>7.6211372531147341E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -1795,7 +1784,7 @@
         <v>7.7086247092713412E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24">
       <c r="A7" t="s">
         <v>66</v>
       </c>
@@ -1866,7 +1855,7 @@
         <v>7.5952162222981219E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24">
       <c r="D8" s="12" t="s">
         <v>14</v>
       </c>
@@ -1930,7 +1919,7 @@
         <v>7.4940275000536802E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24">
       <c r="A9" t="s">
         <v>76</v>
       </c>
@@ -2001,7 +1990,7 @@
         <v>7.5255128544236957E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24">
       <c r="D10" s="12" t="s">
         <v>71</v>
       </c>
@@ -2038,7 +2027,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2072,7 +2061,7 @@
         <v>49096</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24">
       <c r="D12" s="12" t="s">
         <v>73</v>
       </c>
@@ -2099,7 +2088,7 @@
         <v>49461</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24">
       <c r="A13" t="s">
         <v>77</v>
       </c>
@@ -2132,7 +2121,7 @@
         <v>49828</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24">
       <c r="A14" t="s">
         <v>78</v>
       </c>
@@ -2140,7 +2129,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24">
       <c r="A15" t="s">
         <v>80</v>
       </c>
@@ -2148,7 +2137,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -2158,7 +2147,7 @@
       </c>
       <c r="L17" s="1"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
         <v>84</v>
       </c>
@@ -2168,10 +2157,10 @@
       </c>
       <c r="L18" s="1"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12">
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2181,7 +2170,7 @@
       </c>
       <c r="L20" s="1"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2191,10 +2180,10 @@
       </c>
       <c r="L21" s="1"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12">
       <c r="L22" s="1"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -2203,7 +2192,7 @@
       </c>
       <c r="L23" s="1"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12">
       <c r="A24" t="s">
         <v>85</v>
       </c>
@@ -2212,10 +2201,10 @@
       </c>
       <c r="L24" s="1"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12">
       <c r="L25" s="1"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -2225,10 +2214,10 @@
       </c>
       <c r="L26" s="1"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12">
       <c r="L27" s="1"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12">
       <c r="A28" t="s">
         <v>89</v>
       </c>
@@ -2237,7 +2226,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R28C2BermudanExercise,A</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12">
       <c r="A30" t="s">
         <v>90</v>
       </c>
@@ -2246,7 +2235,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R30C2Swaption,A</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12">
       <c r="A31" t="s">
         <v>91</v>
       </c>
@@ -2255,7 +2244,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R31C2Swaption,A</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12">
       <c r="A32" t="s">
         <v>92</v>
       </c>
@@ -2264,7 +2253,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R32C2Swaption,A</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
         <v>93</v>
       </c>
@@ -2273,7 +2262,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R33C2Swaption,A</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>94</v>
       </c>
@@ -2282,7 +2271,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R34C2Swaption,A</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
         <v>27</v>
       </c>
@@ -2291,13 +2280,13 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R36C2Swaption,A</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2">
       <c r="B37" s="4"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2">
       <c r="B38" s="4"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2">
       <c r="A39" t="s">
         <v>108</v>
       </c>
@@ -2305,7 +2294,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>96</v>
       </c>
@@ -2314,7 +2303,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R40C2Gsr,A</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2">
       <c r="A41" t="s">
         <v>97</v>
       </c>
@@ -2323,7 +2312,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R41C2Gaussian1dSwaptionEngine,A</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2">
       <c r="A43" t="s">
         <v>99</v>
       </c>
@@ -2332,7 +2321,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R43C2LevenbergMarquardt,A</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
         <v>56</v>
       </c>
@@ -2340,7 +2329,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2">
       <c r="A46" t="s">
         <v>57</v>
       </c>
@@ -2348,7 +2337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2">
       <c r="A47" t="s">
         <v>58</v>
       </c>
@@ -2356,7 +2345,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2">
       <c r="A48" t="s">
         <v>59</v>
       </c>
@@ -2364,7 +2353,7 @@
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>60</v>
       </c>
@@ -2372,7 +2361,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>100</v>
       </c>
@@ -2381,7 +2370,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R50C2EndCriteria,A</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>105</v>
       </c>
@@ -2390,12 +2379,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2">
       <c r="B54" s="12" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>90</v>
       </c>
@@ -2404,7 +2393,7 @@
         <v>21.703395415542996</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2">
       <c r="A56" t="s">
         <v>91</v>
       </c>
@@ -2413,7 +2402,7 @@
         <v>96.520281949826526</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>92</v>
       </c>
@@ -2422,7 +2411,7 @@
         <v>123.61092110729599</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>93</v>
       </c>
@@ -2431,7 +2420,7 @@
         <v>110.33999699797786</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>94</v>
       </c>
@@ -2440,7 +2429,7 @@
         <v>67.704758683639781</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2">
       <c r="A61" t="s">
         <v>27</v>
       </c>
@@ -2449,7 +2438,7 @@
         <v>177.75574893498674</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2">
       <c r="A62" t="s">
         <v>107</v>
       </c>

--- a/tests/workbooktests/workbooks/test_gaussian1dmodel.xlsx
+++ b/tests/workbooktests/workbooks/test_gaussian1dmodel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A211BC-9FBB-4962-BCBB-6ED81D72D173}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878982D3-CC01-4623-869B-AF781D100988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{096EF196-26B4-4940-94D5-2518E57D2FCB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{096EF196-26B4-4940-94D5-2518E57D2FCB}"/>
   </bookViews>
   <sheets>
     <sheet name="GSR Model and Engine" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -29,14 +40,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -387,7 +398,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -813,14 +824,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19C12335-CBD8-46BF-9EBD-5BF6B0C18873}">
   <dimension ref="A1:E80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.375" customWidth="1"/>
-    <col min="3" max="5" width="24.625" customWidth="1"/>
+    <col min="2" max="2" width="35.42578125" customWidth="1"/>
+    <col min="3" max="5" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -828,7 +839,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -837,7 +848,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -846,7 +857,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -864,7 +875,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -881,7 +892,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -898,7 +909,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -906,7 +917,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>7</v>
       </c>
@@ -915,7 +926,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R13C2Gsr,A</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>8</v>
       </c>
@@ -924,7 +935,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R15C2Gaussian1dSwaptionEngine,A</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -933,7 +944,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R17C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -942,10 +953,10 @@
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R18C2Euribor,A</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -953,7 +964,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -961,7 +972,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -970,7 +981,7 @@
         <v>46905</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -979,7 +990,7 @@
         <v>48001</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -987,7 +998,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -996,7 +1007,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R25C2Schedule,A</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -1005,7 +1016,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R26C2Schedule,A</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1014,42 +1025,42 @@
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R27C2VanillaSwap,A</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B28" s="4"/>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="1" cm="1">
         <f t="array" ref="B29:B33">_xll.qlScheduleDates(B25) - 2</f>
         <v>46903</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B30" s="3">
         <v>46904</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B31" s="3">
         <v>47271</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B32" s="3">
         <v>47635</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B33" s="6">
         <v>47999</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B34" s="4"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>22</v>
       </c>
@@ -1058,7 +1069,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R35C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>23</v>
       </c>
@@ -1067,25 +1078,25 @@
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R36C2BermudanExercise,A</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B37" s="4"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>24</v>
       </c>
       <c r="B38" s="4"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>25</v>
       </c>
       <c r="B39" s="4"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B40" s="4"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>26</v>
       </c>
@@ -1094,7 +1105,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R41C2Swaption,A</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -1103,7 +1114,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R42C2Swaption,A</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>28</v>
       </c>
@@ -1112,7 +1123,7 @@
         <v>126.78027860072075</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>28</v>
       </c>
@@ -1121,7 +1132,7 @@
         <v>125.42646852011532</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B48" s="10" t="s">
         <v>29</v>
       </c>
@@ -1135,7 +1146,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>30</v>
       </c>
@@ -1152,7 +1163,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>32</v>
       </c>
@@ -1169,7 +1180,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>34</v>
       </c>
@@ -1186,7 +1197,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>35</v>
       </c>
@@ -1207,7 +1218,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R18C2Euribor,A</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>36</v>
       </c>
@@ -1224,7 +1235,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>38</v>
       </c>
@@ -1241,7 +1252,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>40</v>
       </c>
@@ -1258,7 +1269,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>42</v>
       </c>
@@ -1279,7 +1290,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>43</v>
       </c>
@@ -1296,7 +1307,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>45</v>
       </c>
@@ -1313,7 +1324,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>46</v>
       </c>
@@ -1330,7 +1341,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>47</v>
       </c>
@@ -1347,7 +1358,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>49</v>
       </c>
@@ -1364,7 +1375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>50</v>
       </c>
@@ -1381,7 +1392,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>51</v>
       </c>
@@ -1398,7 +1409,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>29</v>
       </c>
@@ -1419,7 +1430,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R65C5SwaptionHelper,A</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B66" t="b">
         <f t="array" ref="B66">_xll.qlBlackCalibrationHelperSetPricingEngine(B65,$B$15)</f>
         <v>1</v>
@@ -1437,7 +1448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>55</v>
       </c>
@@ -1446,7 +1457,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R68C2LevenbergMarquardt,A</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>56</v>
       </c>
@@ -1454,7 +1465,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>57</v>
       </c>
@@ -1462,7 +1473,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>58</v>
       </c>
@@ -1470,7 +1481,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>59</v>
       </c>
@@ -1478,7 +1489,7 @@
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>60</v>
       </c>
@@ -1486,7 +1497,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>61</v>
       </c>
@@ -1495,7 +1506,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R75C2EndCriteria,A</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>62</v>
       </c>
@@ -1504,11 +1515,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="15">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B79">
+      <c r="B79" cm="1">
         <f t="array" ref="B79:E79">TRANSPOSE(_xll.qlGsrVolatility(B13,B77))</f>
         <v>6.9631874311834709E-3</v>
       </c>
@@ -1522,11 +1533,11 @@
         <v>6.999176212400815E-3</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B80">
+      <c r="B80" cm="1">
         <f t="array" ref="B80:E80">TRANSPOSE(_xll.qlGsrReversion(B13,B77))</f>
         <v>0.01</v>
       </c>
@@ -1548,24 +1559,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3DE146D-E077-4092-A23A-A651D070976A}">
   <dimension ref="A1:X62"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.625" customWidth="1"/>
-    <col min="2" max="2" width="28.625" customWidth="1"/>
-    <col min="4" max="4" width="17.75" customWidth="1"/>
-    <col min="11" max="11" width="14.25" customWidth="1"/>
-    <col min="15" max="15" width="14.75" customWidth="1"/>
-    <col min="16" max="16" width="12.125" customWidth="1"/>
-    <col min="17" max="18" width="13.5" customWidth="1"/>
-    <col min="19" max="19" width="13.125" customWidth="1"/>
-    <col min="20" max="20" width="18.5" customWidth="1"/>
+    <col min="1" max="1" width="20.5703125" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" customWidth="1"/>
+    <col min="16" max="16" width="12.140625" customWidth="1"/>
+    <col min="17" max="18" width="13.42578125" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" customWidth="1"/>
+    <col min="20" max="20" width="18.42578125" customWidth="1"/>
     <col min="21" max="21" width="15" customWidth="1"/>
-    <col min="22" max="22" width="13.25" customWidth="1"/>
-    <col min="23" max="23" width="11.375" customWidth="1"/>
-    <col min="24" max="24" width="10.5" customWidth="1"/>
+    <col min="22" max="22" width="13.28515625" customWidth="1"/>
+    <col min="23" max="23" width="11.42578125" customWidth="1"/>
+    <col min="24" max="24" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1573,7 +1584,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1582,7 +1593,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>82</v>
       </c>
@@ -1647,7 +1658,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="D5" s="12" t="s">
         <v>12</v>
       </c>
@@ -1713,7 +1724,7 @@
         <v>7.6211372531147341E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -1784,7 +1795,7 @@
         <v>7.7086247092713412E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>66</v>
       </c>
@@ -1855,7 +1866,7 @@
         <v>7.5952162222981219E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="D8" s="12" t="s">
         <v>14</v>
       </c>
@@ -1919,7 +1930,7 @@
         <v>7.4940275000536802E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>76</v>
       </c>
@@ -1990,7 +2001,7 @@
         <v>7.5255128544236957E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="D10" s="12" t="s">
         <v>71</v>
       </c>
@@ -2027,7 +2038,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2061,7 +2072,7 @@
         <v>49096</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="D12" s="12" t="s">
         <v>73</v>
       </c>
@@ -2088,7 +2099,7 @@
         <v>49461</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>77</v>
       </c>
@@ -2121,7 +2132,7 @@
         <v>49828</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>78</v>
       </c>
@@ -2129,7 +2140,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>80</v>
       </c>
@@ -2137,7 +2148,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -2147,7 +2158,7 @@
       </c>
       <c r="L17" s="1"/>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>84</v>
       </c>
@@ -2157,10 +2168,10 @@
       </c>
       <c r="L18" s="1"/>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2170,7 +2181,7 @@
       </c>
       <c r="L20" s="1"/>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2180,10 +2191,10 @@
       </c>
       <c r="L21" s="1"/>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L22" s="1"/>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -2192,7 +2203,7 @@
       </c>
       <c r="L23" s="1"/>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>85</v>
       </c>
@@ -2201,10 +2212,10 @@
       </c>
       <c r="L24" s="1"/>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L25" s="1"/>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -2214,10 +2225,10 @@
       </c>
       <c r="L26" s="1"/>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L27" s="1"/>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>89</v>
       </c>
@@ -2226,7 +2237,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R28C2BermudanExercise,A</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>90</v>
       </c>
@@ -2235,7 +2246,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R30C2Swaption,A</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>91</v>
       </c>
@@ -2244,7 +2255,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R31C2Swaption,A</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>92</v>
       </c>
@@ -2253,7 +2264,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R32C2Swaption,A</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>93</v>
       </c>
@@ -2262,7 +2273,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R33C2Swaption,A</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>94</v>
       </c>
@@ -2271,7 +2282,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R34C2Swaption,A</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>27</v>
       </c>
@@ -2280,13 +2291,13 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R36C2Swaption,A</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B37" s="4"/>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B38" s="4"/>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>108</v>
       </c>
@@ -2294,7 +2305,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>96</v>
       </c>
@@ -2303,7 +2314,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R40C2Gsr,A</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>97</v>
       </c>
@@ -2312,7 +2323,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R41C2Gaussian1dSwaptionEngine,A</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>99</v>
       </c>
@@ -2321,7 +2332,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R43C2LevenbergMarquardt,A</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>56</v>
       </c>
@@ -2329,7 +2340,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>57</v>
       </c>
@@ -2337,7 +2348,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>58</v>
       </c>
@@ -2345,7 +2356,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>59</v>
       </c>
@@ -2353,7 +2364,7 @@
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>60</v>
       </c>
@@ -2361,7 +2372,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>100</v>
       </c>
@@ -2370,7 +2381,7 @@
         <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R50C2EndCriteria,A</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>105</v>
       </c>
@@ -2379,12 +2390,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B54" s="12" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>90</v>
       </c>
@@ -2393,7 +2404,7 @@
         <v>21.703395415542996</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>91</v>
       </c>
@@ -2402,7 +2413,7 @@
         <v>96.520281949826526</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>92</v>
       </c>
@@ -2411,7 +2422,7 @@
         <v>123.61092110729599</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>93</v>
       </c>
@@ -2420,7 +2431,7 @@
         <v>110.33999699797786</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>94</v>
       </c>
@@ -2429,7 +2440,7 @@
         <v>67.704758683639781</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>27</v>
       </c>
@@ -2438,7 +2449,7 @@
         <v>177.75574893498674</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>107</v>
       </c>
